--- a/examples/07_hsr_140km/01_Infrastructure.xlsx
+++ b/examples/07_hsr_140km/01_Infrastructure.xlsx
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>NOMINAL</t>
+          <t>BIDIRECTIONAL</t>
         </is>
       </c>
     </row>
